--- a/excel/common.xlsx
+++ b/excel/common.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
   <si>
     <t>编号</t>
   </si>
@@ -71,6 +71,111 @@
   </si>
   <si>
     <t>通用</t>
+  </si>
+  <si>
+    <t>loadCircleTime</t>
+  </si>
+  <si>
+    <t>搜索物品加载单圈时间</t>
+  </si>
+  <si>
+    <t>drugDrugCount</t>
+  </si>
+  <si>
+    <t>小药品初始数量</t>
+  </si>
+  <si>
+    <t>drugDrugHp</t>
+  </si>
+  <si>
+    <t>小药品恢复血量百分比</t>
+  </si>
+  <si>
+    <t>drugDrugAdCount</t>
+  </si>
+  <si>
+    <t>小药品广告赠送数量</t>
+  </si>
+  <si>
+    <t>drugDrugUseTime</t>
+  </si>
+  <si>
+    <t>小药品使用时间（秒）</t>
+  </si>
+  <si>
+    <t>drugDrugCountBig</t>
+  </si>
+  <si>
+    <t>大药品初始数量</t>
+  </si>
+  <si>
+    <t>drugDrugHpBig</t>
+  </si>
+  <si>
+    <t>大药品恢复血量百分比</t>
+  </si>
+  <si>
+    <t>drugDrugAdCountBig</t>
+  </si>
+  <si>
+    <t>大药品广告赠送数量</t>
+  </si>
+  <si>
+    <t>drugDrugUseTimeBig</t>
+  </si>
+  <si>
+    <t>大药品使用时间（秒）</t>
+  </si>
+  <si>
+    <t>leaveTime</t>
+  </si>
+  <si>
+    <t>撤离时间（秒）</t>
+  </si>
+  <si>
+    <t>gunResetTime</t>
+  </si>
+  <si>
+    <t>枪口回正时间（秒）</t>
+  </si>
+  <si>
+    <t>玩家</t>
+  </si>
+  <si>
+    <t>patrolWaitTime</t>
+  </si>
+  <si>
+    <t>[2, 5]</t>
+  </si>
+  <si>
+    <t>巡逻等待时间（秒）</t>
+  </si>
+  <si>
+    <t>小兵</t>
+  </si>
+  <si>
+    <t>npcAttackPercent</t>
+  </si>
+  <si>
+    <t>npc小兵攻击力百分比</t>
+  </si>
+  <si>
+    <t>npcSpeedPercent</t>
+  </si>
+  <si>
+    <t>npc小兵速度百分比</t>
+  </si>
+  <si>
+    <t>npcAttackRangePercent</t>
+  </si>
+  <si>
+    <t>npc小兵的攻击范围百分比</t>
+  </si>
+  <si>
+    <t>npcFireRatePercent</t>
+  </si>
+  <si>
+    <t>npc小兵的射速百分比</t>
   </si>
 </sst>
 </file>
@@ -1113,141 +1218,333 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="4">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
+      <c r="A9" s="3">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
+      <c r="A10" s="3">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
+      <c r="A11" s="3">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="4">
+        <v>100</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
+      <c r="A12" s="3">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
+      <c r="A13" s="3">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="4">
+        <v>4</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
+      <c r="A14" s="3">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="4">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
+      <c r="A15" s="3">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="A16" s="3">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="4">
+        <v>20</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="4">
+        <v>80</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="4">
+        <v>80</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="4">
+        <v>80</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:5">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:5">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:5">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:5">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:5">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:5">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:5">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:5">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:5">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:5">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:5">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>

--- a/excel/common.xlsx
+++ b/excel/common.xlsx
@@ -79,49 +79,49 @@
     <t>搜索物品加载单圈时间</t>
   </si>
   <si>
-    <t>drugDrugCount</t>
+    <t>drugCount</t>
   </si>
   <si>
     <t>小药品初始数量</t>
   </si>
   <si>
-    <t>drugDrugHp</t>
+    <t>drugHp</t>
   </si>
   <si>
     <t>小药品恢复血量百分比</t>
   </si>
   <si>
-    <t>drugDrugAdCount</t>
+    <t>drugAdCount</t>
   </si>
   <si>
     <t>小药品广告赠送数量</t>
   </si>
   <si>
-    <t>drugDrugUseTime</t>
+    <t>drugUseTime</t>
   </si>
   <si>
     <t>小药品使用时间（秒）</t>
   </si>
   <si>
-    <t>drugDrugCountBig</t>
+    <t>drugCountBig</t>
   </si>
   <si>
     <t>大药品初始数量</t>
   </si>
   <si>
-    <t>drugDrugHpBig</t>
+    <t>drugHpBig</t>
   </si>
   <si>
     <t>大药品恢复血量百分比</t>
   </si>
   <si>
-    <t>drugDrugAdCountBig</t>
+    <t>drugAdCountBig</t>
   </si>
   <si>
     <t>大药品广告赠送数量</t>
   </si>
   <si>
-    <t>drugDrugUseTimeBig</t>
+    <t>drugUseTimeBig</t>
   </si>
   <si>
     <t>大药品使用时间（秒）</t>

--- a/excel/common.xlsx
+++ b/excel/common.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
   <si>
     <t>编号</t>
   </si>
@@ -176,6 +176,12 @@
   </si>
   <si>
     <t>npc小兵的射速百分比</t>
+  </si>
+  <si>
+    <t>equipmentSellPercent</t>
+  </si>
+  <si>
+    <t>装备售卖百分比</t>
   </si>
 </sst>
 </file>
@@ -1490,9 +1496,21 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
+      <c r="A21" s="3">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="4">
+        <v>60</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="4"/>

--- a/excel/common.xlsx
+++ b/excel/common.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="65">
   <si>
     <t>编号</t>
   </si>
@@ -182,6 +182,54 @@
   </si>
   <si>
     <t>装备售卖百分比</t>
+  </si>
+  <si>
+    <t>attackRangePercent</t>
+  </si>
+  <si>
+    <t>[2, 30]</t>
+  </si>
+  <si>
+    <t>攻击力区间</t>
+  </si>
+  <si>
+    <t>武器</t>
+  </si>
+  <si>
+    <t>attackIntervalRangePercent</t>
+  </si>
+  <si>
+    <t>[0, 1.5]</t>
+  </si>
+  <si>
+    <t>攻速区间</t>
+  </si>
+  <si>
+    <t>capacityRangePercent</t>
+  </si>
+  <si>
+    <t>[0, 90]</t>
+  </si>
+  <si>
+    <t>弹夹容量区间</t>
+  </si>
+  <si>
+    <t>attackRangeRangePercent</t>
+  </si>
+  <si>
+    <t>[50, 700]</t>
+  </si>
+  <si>
+    <t>射程区间</t>
+  </si>
+  <si>
+    <t>speedRangePercent</t>
+  </si>
+  <si>
+    <t>[0, 1]</t>
+  </si>
+  <si>
+    <t>移速区间</t>
   </si>
 </sst>
 </file>
@@ -1513,29 +1561,89 @@
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
+      <c r="A22" s="3">
+        <v>18</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
+      <c r="A23" s="3">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
+      <c r="A24" s="3">
+        <v>20</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
+      <c r="A25" s="3">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
+      <c r="A26" s="3">
+        <v>22</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="4"/>

--- a/excel/common.xlsx
+++ b/excel/common.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="73">
   <si>
     <t>编号</t>
   </si>
@@ -230,6 +230,30 @@
   </si>
   <si>
     <t>移速区间</t>
+  </si>
+  <si>
+    <t>背包容量区间</t>
+  </si>
+  <si>
+    <t>装备</t>
+  </si>
+  <si>
+    <t>armorRangePercent</t>
+  </si>
+  <si>
+    <t>[0,100]</t>
+  </si>
+  <si>
+    <t>护甲值区间</t>
+  </si>
+  <si>
+    <t>invincibleRangePercent</t>
+  </si>
+  <si>
+    <t>[0, 60]</t>
+  </si>
+  <si>
+    <t>免伤区间</t>
   </si>
 </sst>
 </file>
@@ -1646,19 +1670,55 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
+      <c r="A27" s="3">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
+      <c r="A28" s="3">
+        <v>24</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
+      <c r="A29" s="3">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4"/>

--- a/excel/common.xlsx
+++ b/excel/common.xlsx
@@ -226,7 +226,7 @@
     <t>speedRangePercent</t>
   </si>
   <si>
-    <t>[0, 1]</t>
+    <t>[0, 100]</t>
   </si>
   <si>
     <t>移速区间</t>

--- a/excel/common.xlsx
+++ b/excel/common.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
   <si>
     <t>编号</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>value</t>
+  </si>
+  <si>
+    <t>int</t>
   </si>
   <si>
     <t>string</t>
@@ -1272,10 +1275,10 @@
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1283,16 +1286,16 @@
         <v>0</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="4">
         <v>300</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1300,16 +1303,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4">
         <v>0.5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1317,16 +1320,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="4">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1334,16 +1337,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="4">
         <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1351,16 +1354,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="4">
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1368,16 +1371,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" s="4">
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1385,16 +1388,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="4">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1402,16 +1405,16 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" s="4">
         <v>100</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1419,16 +1422,16 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" s="4">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1436,16 +1439,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="4">
         <v>4</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1453,16 +1456,16 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="4">
         <v>10</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1470,16 +1473,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" s="4">
         <v>1</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1487,16 +1490,16 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1504,16 +1507,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C17" s="4">
         <v>20</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1521,16 +1524,16 @@
         <v>14</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C18" s="4">
         <v>80</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1538,16 +1541,16 @@
         <v>15</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C19" s="4">
         <v>80</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1555,16 +1558,16 @@
         <v>16</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" s="4">
         <v>80</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1572,16 +1575,16 @@
         <v>17</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C21" s="4">
         <v>60</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1589,16 +1592,16 @@
         <v>18</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1606,16 +1609,16 @@
         <v>19</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1623,16 +1626,16 @@
         <v>20</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1640,16 +1643,16 @@
         <v>21</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1657,16 +1660,16 @@
         <v>22</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1674,16 +1677,16 @@
         <v>23</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1691,16 +1694,16 @@
         <v>24</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1708,16 +1711,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:5">

--- a/excel/common.xlsx
+++ b/excel/common.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="77">
   <si>
     <t>编号</t>
   </si>
@@ -257,6 +257,15 @@
   </si>
   <si>
     <t>免伤区间</t>
+  </si>
+  <si>
+    <t>collectionBookGold</t>
+  </si>
+  <si>
+    <t>[1, 2, 3, 5, 10]</t>
+  </si>
+  <si>
+    <t>收藏品图鉴金币</t>
   </si>
 </sst>
 </file>
@@ -1724,9 +1733,21 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
+      <c r="A30" s="3">
+        <v>26</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4"/>

--- a/excel/common.xlsx
+++ b/excel/common.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="79">
   <si>
     <t>编号</t>
   </si>
@@ -266,6 +266,12 @@
   </si>
   <si>
     <t>收藏品图鉴金币</t>
+  </si>
+  <si>
+    <t>goldToMoney</t>
+  </si>
+  <si>
+    <t>金币银币换算系数</t>
   </si>
 </sst>
 </file>
@@ -1468,7 +1474,7 @@
         <v>31</v>
       </c>
       <c r="C14" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>32</v>
@@ -1519,7 +1525,7 @@
         <v>40</v>
       </c>
       <c r="C17" s="4">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>41</v>
@@ -1750,9 +1756,21 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
+      <c r="A31" s="3">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="4">
+        <v>10000</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="4"/>

--- a/excel/common.xlsx
+++ b/excel/common.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$C$547</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$C$546</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="77">
   <si>
     <t>编号</t>
   </si>
@@ -161,12 +161,6 @@
   </si>
   <si>
     <t>npc小兵攻击力百分比</t>
-  </si>
-  <si>
-    <t>npcSpeedPercent</t>
-  </si>
-  <si>
-    <t>npc小兵速度百分比</t>
   </si>
   <si>
     <t>npcAttackRangePercent</t>
@@ -1247,7 +1241,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E546"/>
+  <dimension ref="A1:E545"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="25.125" style="1" customWidth="1"/>
@@ -1536,7 +1530,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>42</v>
@@ -1553,7 +1547,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>44</v>
@@ -1570,183 +1564,183 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C20" s="4">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>39</v>
+      <c r="E20" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="4">
-        <v>60</v>
+      <c r="C21" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" s="4" t="s">
         <v>73</v>
       </c>
+      <c r="D29" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="E29" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C30" s="4" t="s">
         <v>75</v>
+      </c>
+      <c r="C30" s="4">
+        <v>10000</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>76</v>
@@ -1756,21 +1750,9 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="3">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="4">
-        <v>10000</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="4"/>
@@ -3479,8 +3461,6 @@
     </row>
     <row r="373" spans="1:3">
       <c r="A373" s="4"/>
-      <c r="B373" s="4"/>
-      <c r="C373" s="4"/>
     </row>
     <row r="374" spans="1:3">
       <c r="A374" s="4"/>
@@ -3998,11 +3978,8 @@
     <row r="545" spans="1:1">
       <c r="A545" s="4"/>
     </row>
-    <row r="546" spans="1:1">
-      <c r="A546" s="4"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:C547" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:C546" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/common.xlsx
+++ b/excel/common.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameSVN\game003\cocosProject\escape\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\svn\game003\cocosProject\escape\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12360"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="78">
   <si>
     <t>编号</t>
   </si>
@@ -184,7 +184,7 @@
     <t>attackRangePercent</t>
   </si>
   <si>
-    <t>[2, 30]</t>
+    <t>[5,120]</t>
   </si>
   <si>
     <t>攻击力区间</t>
@@ -196,7 +196,7 @@
     <t>attackIntervalRangePercent</t>
   </si>
   <si>
-    <t>[0, 1.5]</t>
+    <t>[0, 1.0]</t>
   </si>
   <si>
     <t>攻速区间</t>
@@ -205,28 +205,31 @@
     <t>capacityRangePercent</t>
   </si>
   <si>
+    <t>[0, 80]</t>
+  </si>
+  <si>
+    <t>弹夹容量区间</t>
+  </si>
+  <si>
+    <t>attackRangeRangePercent</t>
+  </si>
+  <si>
+    <t>[50, 1000]</t>
+  </si>
+  <si>
+    <t>射程区间</t>
+  </si>
+  <si>
+    <t>speedRangePercent</t>
+  </si>
+  <si>
+    <t>[0, 100]</t>
+  </si>
+  <si>
+    <t>移速区间</t>
+  </si>
+  <si>
     <t>[0, 90]</t>
-  </si>
-  <si>
-    <t>弹夹容量区间</t>
-  </si>
-  <si>
-    <t>attackRangeRangePercent</t>
-  </si>
-  <si>
-    <t>[50, 700]</t>
-  </si>
-  <si>
-    <t>射程区间</t>
-  </si>
-  <si>
-    <t>speedRangePercent</t>
-  </si>
-  <si>
-    <t>[0, 100]</t>
-  </si>
-  <si>
-    <t>移速区间</t>
   </si>
   <si>
     <t>背包容量区间</t>
@@ -1672,13 +1675,13 @@
         <v>55</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1686,16 +1689,16 @@
         <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1703,16 +1706,16 @@
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1720,13 +1723,13 @@
         <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>12</v>
@@ -1737,13 +1740,13 @@
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C30" s="4">
         <v>10000</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>12</v>
